--- a/output/encoding_latin_1_file_0.xlsx
+++ b/output/encoding_latin_1_file_0.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>any_comment</t>
         </is>
       </c>
     </row>
